--- a/data/trans_dic/P39A4_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P39A4_2023-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que estar con dolor o malestar en los brazos o en el pecho es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que estar con dolor o malestar en los brazos o en el pecho es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 92,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>84,49; 95,18</t>
+          <t>84,22; 94,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>93,84; 97,22</t>
+          <t>93,81; 97,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>89,51; 95,64</t>
+          <t>89,26; 95,47</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>94,57; 99,08</t>
+          <t>94,64; 99,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>95,89; 98,49</t>
+          <t>95,9; 98,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>96,02; 98,58</t>
+          <t>96,11; 98,48</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>87,81; 94,0</t>
+          <t>87,82; 94,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>84,35; 90,41</t>
+          <t>84,5; 90,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>87,33; 91,6</t>
+          <t>87,13; 91,55</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>95,48; 99,44</t>
+          <t>95,81; 99,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42,97; 97,1</t>
+          <t>44,65; 96,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60,01; 97,63</t>
+          <t>59,72; 97,62</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>99,3; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>94,73; 99,27</t>
+          <t>94,04; 99,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>96,79; 99,62</t>
+          <t>96,71; 99,62</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>91,88; 97,34</t>
+          <t>91,72; 97,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>93,78; 98,25</t>
+          <t>94,02; 98,39</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>94,02; 97,39</t>
+          <t>93,98; 97,42</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>74,64; 82,78</t>
+          <t>75,28; 82,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>80,37; 93,45</t>
+          <t>80,21; 93,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>79,22; 89,36</t>
+          <t>79,48; 89,68</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>94,84; 98,78</t>
+          <t>94,8; 98,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>95,97; 98,0</t>
+          <t>95,95; 98,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>95,82; 98,34</t>
+          <t>95,79; 98,27</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>91,53; 94,55</t>
+          <t>91,62; 94,57</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>83,21; 93,75</t>
+          <t>84,46; 93,82</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>88,25; 93,4</t>
+          <t>88,71; 93,49</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que estar con dolor o malestar en los brazos o en el pecho es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que estar con dolor o malestar en los brazos o en el pecho es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 92,53%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>262530; 295745</t>
+          <t>261694; 294902</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>266359; 275965</t>
+          <t>266295; 275989</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>532200; 568633</t>
+          <t>530736; 567632</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>483448; 506496</t>
+          <t>483817; 507123</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>479167; 492173</t>
+          <t>479213; 492180</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>970659; 996589</t>
+          <t>971616; 995564</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>260443; 278810</t>
+          <t>260454; 279019</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>270863; 290332</t>
+          <t>271330; 291247</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>539443; 565795</t>
+          <t>538212; 565517</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>238778; 248670</t>
+          <t>239588; 248647</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>164165; 370981</t>
+          <t>170589; 370518</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>379367; 617146</t>
+          <t>377508; 617077</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>174134; 175367</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>193775; 203064</t>
+          <t>192360; 203212</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>367727; 378472</t>
+          <t>367411; 378469</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>228398; 241953</t>
+          <t>227978; 242374</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>215628; 225892</t>
+          <t>216183; 226222</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>449868; 466009</t>
+          <t>449687; 466168</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>450946; 500121</t>
+          <t>454813; 498906</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>657715; 764740</t>
+          <t>656396; 765502</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1126963; 1271130</t>
+          <t>1130638; 1275769</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>799418; 832597</t>
+          <t>799078; 833239</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>629035; 642383</t>
+          <t>628904; 642551</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1435728; 1473404</t>
+          <t>1435200; 1472428</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2965068; 3063135</t>
+          <t>2968242; 3063766</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2824859; 3182742</t>
+          <t>2867313; 3185179</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5855033; 6196508</t>
+          <t>5885563; 6202989</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P39A4_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P39A4_2023-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,61%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>84,22; 94,91</t>
+          <t>88,65; 95,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>93,81; 97,23</t>
+          <t>90,96; 96,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>89,26; 95,47</t>
+          <t>91,27; 95,36</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>94,64; 99,2</t>
+          <t>95,55; 99,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>95,9; 98,49</t>
+          <t>95,97; 98,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>96,11; 98,48</t>
+          <t>96,5; 98,61</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,1%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>87,82; 94,08</t>
+          <t>88,21; 94,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>84,5; 90,7</t>
+          <t>83,35; 89,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>87,13; 91,55</t>
+          <t>86,72; 91,0</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>95,81; 99,43</t>
+          <t>91,75; 98,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>44,65; 96,98</t>
+          <t>93,67; 97,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59,72; 97,62</t>
+          <t>94,31; 97,83</t>
         </is>
       </c>
     </row>
@@ -754,12 +754,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -777,12 +777,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>94,04; 99,35</t>
+          <t>95,43; 99,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>96,71; 99,62</t>
+          <t>97,68; 99,8</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,81%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>91,72; 97,51</t>
+          <t>92,08; 97,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>94,02; 98,39</t>
+          <t>93,31; 97,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>93,98; 97,42</t>
+          <t>93,82; 97,18</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>79,01%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>75,28; 82,58</t>
+          <t>73,77; 81,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>80,21; 93,54</t>
+          <t>77,17; 82,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>79,48; 89,68</t>
+          <t>76,41; 81,18</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,34%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>94,8; 98,86</t>
+          <t>93,61; 97,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>95,95; 98,03</t>
+          <t>95,66; 97,96</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>95,79; 98,27</t>
+          <t>95,18; 97,19</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,1%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>91,62; 94,57</t>
+          <t>90,75; 93,01</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>84,46; 93,82</t>
+          <t>91,47; 93,1</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>88,71; 93,49</t>
+          <t>91,33; 92,76</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>284109</t>
+          <t>295449</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>271919</t>
+          <t>294588</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>556028</t>
+          <t>590037</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>261694; 294902</t>
+          <t>281986; 304221</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>266295; 275989</t>
+          <t>283996; 300706</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>530736; 567632</t>
+          <t>575274; 601079</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>500461</t>
+          <t>511708</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>486767</t>
+          <t>516176</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>987228</t>
+          <t>1027882</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>483817; 507123</t>
+          <t>498754; 518286</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>479213; 492180</t>
+          <t>508214; 521034</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>971616; 995564</t>
+          <t>1014723; 1036902</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>270626</t>
+          <t>271052</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>281994</t>
+          <t>283269</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>552621</t>
+          <t>554321</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>260454; 279019</t>
+          <t>261304; 279232</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>271330; 291247</t>
+          <t>271641; 292680</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>538212; 565517</t>
+          <t>539506; 566140</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>245620</t>
+          <t>279229</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>301439</t>
+          <t>335035</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>547060</t>
+          <t>614264</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>239588; 248647</t>
+          <t>264785; 285359</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>170589; 370518</t>
+          <t>326205; 340635</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>377508; 617077</t>
+          <t>600591; 622984</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>175367</t>
+          <t>197438</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>200142</t>
+          <t>219053</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>375509</t>
+          <t>416491</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>192360; 203212</t>
+          <t>212444; 221431</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>367411; 378469</t>
+          <t>410328; 419220</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>236816</t>
+          <t>233451</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>222651</t>
+          <t>226802</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>459466</t>
+          <t>460254</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>227978; 242374</t>
+          <t>225417; 238605</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>216183; 226222</t>
+          <t>219799; 230672</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>449687; 466168</t>
+          <t>450684; 466840</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>478647</t>
+          <t>539985</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>703749</t>
+          <t>585923</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1182396</t>
+          <t>1125907</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>454813; 498906</t>
+          <t>513047; 564620</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>656396; 765502</t>
+          <t>563056; 604310</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1130638; 1275769</t>
+          <t>1088849; 1156889</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>816609</t>
+          <t>662529</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>636402</t>
+          <t>729238</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1453011</t>
+          <t>1391767</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>799078; 833239</t>
+          <t>647711; 673300</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>628904; 642551</t>
+          <t>719977; 737334</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1435200; 1472428</t>
+          <t>1374995; 1404062</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>3008256</t>
+          <t>2990841</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3105063</t>
+          <t>3190083</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6113319</t>
+          <t>6180923</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2968242; 3063766</t>
+          <t>2953393; 3027169</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2867313; 3185179</t>
+          <t>3161598; 3217929</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5885563; 6202989</t>
+          <t>6128895; 6224926</t>
         </is>
       </c>
     </row>
